--- a/docs/StructureDefinition-actigraphy-observation.xlsx
+++ b/docs/StructureDefinition-actigraphy-observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-actigraphy-observation.xlsx
+++ b/docs/StructureDefinition-actigraphy-observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3651" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3652" uniqueCount="561">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/actigraphy-observation</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/actigraphy-observation</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -471,7 +474,7 @@
     <t>missionContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/mission-context}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mission-context}
 </t>
   </si>
   <si>
@@ -491,7 +494,7 @@
     <t>flightDay</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://mitre.org/fhir/space-health/StructureDefinition/flight-day}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/flight-day}
 </t>
   </si>
   <si>
@@ -702,7 +705,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/ValueSet/actigraphy-metric-vs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/ValueSet/actigraphy-metric-vs</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -726,7 +729,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://mitre.org/fhir/space-health/StructureDefinition/Astronaut)
+    <t xml:space="preserve">Reference(https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/astronaut)
 </t>
   </si>
   <si>
@@ -1497,7 +1500,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://mitre.org/fhir/space-health/CodeSystem/actigraphy-metric-cs"/&gt;
+    &lt;system value="https://awatson1978.github.io/aerospace-medicine-ig/CodeSystem/actigraphy-metric-cs"/&gt;
     &lt;code value="activity-count"/&gt;
     &lt;display value="Activity Count"/&gt;
   &lt;/coding&gt;
@@ -1743,7 +1746,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://mitre.org/fhir/space-health/CodeSystem/actigraphy-metric-cs"/&gt;
+    &lt;system value="https://awatson1978.github.io/aerospace-medicine-ig/CodeSystem/actigraphy-metric-cs"/&gt;
     &lt;code value="rest-activity-ratio"/&gt;
     &lt;display value="Rest-Activity Ratio"/&gt;
   &lt;/coding&gt;
@@ -2040,54 +2043,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2125,7 +2130,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="53.24609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="68.11328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
@@ -2145,149 +2150,149 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -2299,16 +2304,16 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -2358,31 +2363,31 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>20</v>
@@ -2393,10 +2398,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2404,10 +2409,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -2416,19 +2421,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2478,13 +2483,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2513,10 +2518,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2524,10 +2529,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2536,16 +2541,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2596,19 +2601,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2631,10 +2636,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2642,31 +2647,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2716,19 +2721,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2751,10 +2756,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2762,10 +2767,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2777,16 +2782,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2812,13 +2817,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2836,19 +2841,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2871,21 +2876,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2897,16 +2902,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2956,19 +2961,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2980,7 +2985,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>20</v>
@@ -2991,21 +2996,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -3017,16 +3022,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3076,13 +3081,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -3100,7 +3105,7 @@
         <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>20</v>
@@ -3111,10 +3116,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3122,10 +3127,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -3137,13 +3142,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -3182,29 +3187,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -3227,26 +3232,26 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -3255,13 +3260,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3312,19 +3317,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -3347,26 +3352,26 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>20</v>
@@ -3375,13 +3380,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3432,19 +3437,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -3467,45 +3472,45 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3554,19 +3559,19 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
@@ -3578,7 +3583,7 @@
         <v>20</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>20</v>
@@ -3589,10 +3594,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3600,10 +3605,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -3612,20 +3617,20 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -3674,34 +3679,34 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>20</v>
@@ -3709,21 +3714,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -3732,20 +3737,20 @@
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3794,31 +3799,31 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>20</v>
@@ -3829,21 +3834,21 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3852,19 +3857,19 @@
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3914,31 +3919,31 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>20</v>
@@ -3949,10 +3954,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3960,34 +3965,34 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -4012,13 +4017,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -4036,34 +4041,34 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>20</v>
@@ -4071,10 +4076,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4082,13 +4087,13 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>20</v>
@@ -4097,19 +4102,19 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -4134,13 +4139,13 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -4158,19 +4163,19 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
@@ -4182,10 +4187,10 @@
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>20</v>
@@ -4193,45 +4198,45 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -4256,11 +4261,11 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -4278,45 +4283,45 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4324,34 +4329,34 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4400,34 +4405,34 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>20</v>
@@ -4435,10 +4440,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4446,10 +4451,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -4458,19 +4463,19 @@
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4520,34 +4525,34 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>20</v>
@@ -4555,21 +4560,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4578,22 +4583,22 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4642,34 +4647,34 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>20</v>
@@ -4677,45 +4682,45 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4764,34 +4769,34 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>20</v>
@@ -4799,10 +4804,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4810,10 +4815,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4822,19 +4827,19 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4884,19 +4889,19 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
@@ -4905,13 +4910,13 @@
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>20</v>
@@ -4919,10 +4924,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4930,10 +4935,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4942,20 +4947,20 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -5004,34 +5009,34 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>20</v>
@@ -5039,10 +5044,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5050,34 +5055,34 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -5126,45 +5131,45 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5172,10 +5177,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -5187,19 +5192,19 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5224,13 +5229,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -5248,19 +5253,19 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
@@ -5269,10 +5274,10 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
@@ -5283,21 +5288,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -5309,19 +5314,19 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5346,13 +5351,13 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -5370,45 +5375,45 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5416,10 +5421,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -5431,19 +5436,19 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5492,19 +5497,19 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
@@ -5513,10 +5518,10 @@
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -5527,10 +5532,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5538,10 +5543,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5553,16 +5558,16 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5588,13 +5593,13 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5612,45 +5617,45 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5658,10 +5663,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5673,19 +5678,19 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5710,13 +5715,13 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5734,19 +5739,19 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -5755,10 +5760,10 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -5769,10 +5774,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5780,10 +5785,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5795,16 +5800,16 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5854,45 +5859,45 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5900,13 +5905,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>20</v>
@@ -5915,16 +5920,16 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5974,45 +5979,45 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6020,10 +6025,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -6035,19 +6040,19 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -6096,19 +6101,19 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -6117,10 +6122,10 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
@@ -6131,10 +6136,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6142,10 +6147,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -6157,13 +6162,13 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6214,13 +6219,13 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
@@ -6238,7 +6243,7 @@
         <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -6249,21 +6254,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -6275,16 +6280,16 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6334,19 +6339,19 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
@@ -6358,7 +6363,7 @@
         <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -6369,45 +6374,45 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6456,19 +6461,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -6480,7 +6485,7 @@
         <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6491,10 +6496,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6502,10 +6507,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6517,13 +6522,13 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6574,19 +6579,19 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
@@ -6595,10 +6600,10 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -6609,10 +6614,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6620,10 +6625,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6635,13 +6640,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6692,19 +6697,19 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -6713,10 +6718,10 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6727,10 +6732,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6738,10 +6743,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6753,19 +6758,19 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6790,13 +6795,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6814,31 +6819,31 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -6849,10 +6854,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6860,10 +6865,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6875,19 +6880,19 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6912,13 +6917,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6936,31 +6941,31 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AG40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>402</v>
-      </c>
       <c r="AN40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
@@ -6971,10 +6976,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6982,10 +6987,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6997,17 +7002,17 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -7056,19 +7061,19 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -7080,7 +7085,7 @@
         <v>20</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -7091,10 +7096,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7102,10 +7107,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -7117,13 +7122,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7174,19 +7179,19 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
@@ -7195,10 +7200,10 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -7209,10 +7214,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7220,10 +7225,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -7232,19 +7237,19 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7294,19 +7299,19 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -7315,10 +7320,10 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -7329,10 +7334,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7340,10 +7345,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -7352,19 +7357,19 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7414,19 +7419,19 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -7435,10 +7440,10 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
@@ -7449,10 +7454,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7460,10 +7465,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -7472,22 +7477,22 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7524,29 +7529,29 @@
         <v>20</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -7555,10 +7560,10 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7569,10 +7574,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7580,10 +7585,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -7595,13 +7600,13 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7652,13 +7657,13 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
@@ -7676,7 +7681,7 @@
         <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7687,21 +7692,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -7713,16 +7718,16 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7772,19 +7777,19 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -7796,7 +7801,7 @@
         <v>20</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -7807,45 +7812,45 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7894,19 +7899,19 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
@@ -7918,7 +7923,7 @@
         <v>20</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -7929,10 +7934,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7940,10 +7945,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7952,22 +7957,22 @@
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7992,13 +7997,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -8016,34 +8021,34 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>20</v>
@@ -8051,10 +8056,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8062,10 +8067,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -8074,22 +8079,22 @@
         <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -8138,45 +8143,45 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8184,10 +8189,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -8199,19 +8204,19 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8236,13 +8241,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -8260,19 +8265,19 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
@@ -8281,10 +8286,10 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -8295,21 +8300,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -8321,19 +8326,19 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8358,13 +8363,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -8382,45 +8387,45 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8428,10 +8433,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -8443,19 +8448,19 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8504,19 +8509,19 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
@@ -8525,10 +8530,10 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8539,23 +8544,23 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8564,22 +8569,22 @@
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8628,19 +8633,19 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
@@ -8649,10 +8654,10 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
@@ -8663,10 +8668,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8674,10 +8679,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -8689,13 +8694,13 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8746,13 +8751,13 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
@@ -8770,7 +8775,7 @@
         <v>20</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
@@ -8781,21 +8786,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -8807,16 +8812,16 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8866,19 +8871,19 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8890,7 +8895,7 @@
         <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -8901,45 +8906,45 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8988,19 +8993,19 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
@@ -9012,7 +9017,7 @@
         <v>20</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>20</v>
@@ -9023,10 +9028,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9034,10 +9039,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -9046,22 +9051,22 @@
         <v>20</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -9071,7 +9076,7 @@
         <v>20</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>20</v>
@@ -9086,13 +9091,13 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -9110,34 +9115,34 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>20</v>
@@ -9145,10 +9150,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9156,10 +9161,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -9168,22 +9173,22 @@
         <v>20</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9232,45 +9237,45 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9278,10 +9283,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -9293,19 +9298,19 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9330,13 +9335,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -9354,19 +9359,19 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
@@ -9375,10 +9380,10 @@
         <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
@@ -9389,21 +9394,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -9415,19 +9420,19 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9452,13 +9457,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -9476,45 +9481,45 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9522,10 +9527,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -9537,19 +9542,19 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -9598,19 +9603,19 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>20</v>
@@ -9619,10 +9624,10 @@
         <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>20</v>
@@ -9633,23 +9638,23 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -9658,22 +9663,22 @@
         <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9722,19 +9727,19 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>20</v>
@@ -9743,10 +9748,10 @@
         <v>20</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>20</v>
@@ -9757,10 +9762,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9768,10 +9773,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
@@ -9783,13 +9788,13 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9840,13 +9845,13 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>20</v>
@@ -9864,7 +9869,7 @@
         <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>20</v>
@@ -9875,21 +9880,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
@@ -9901,16 +9906,16 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9960,19 +9965,19 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
@@ -9984,7 +9989,7 @@
         <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
@@ -9995,45 +10000,45 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -10082,19 +10087,19 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
@@ -10106,7 +10111,7 @@
         <v>20</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>20</v>
@@ -10117,10 +10122,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10128,10 +10133,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -10140,22 +10145,22 @@
         <v>20</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -10165,7 +10170,7 @@
         <v>20</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>20</v>
@@ -10180,13 +10185,13 @@
         <v>20</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>20</v>
@@ -10204,34 +10209,34 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>20</v>
@@ -10239,10 +10244,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10250,10 +10255,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
@@ -10262,22 +10267,22 @@
         <v>20</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -10326,45 +10331,45 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10372,10 +10377,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>20</v>
@@ -10387,13 +10392,13 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10444,13 +10449,13 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>20</v>
@@ -10468,7 +10473,7 @@
         <v>20</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>20</v>
@@ -10479,21 +10484,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>20</v>
@@ -10505,16 +10510,16 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10552,31 +10557,31 @@
         <v>20</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>20</v>
@@ -10588,7 +10593,7 @@
         <v>20</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>20</v>
@@ -10599,10 +10604,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10610,10 +10615,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>20</v>
@@ -10622,22 +10627,22 @@
         <v>20</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10686,19 +10691,19 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>20</v>
@@ -10707,10 +10712,10 @@
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
@@ -10721,10 +10726,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10732,38 +10737,38 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q72" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="R72" t="s" s="2">
         <v>20</v>
@@ -10784,13 +10789,13 @@
         <v>20</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>20</v>
@@ -10808,19 +10813,19 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>20</v>
@@ -10829,10 +10834,10 @@
         <v>20</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>20</v>
@@ -10843,10 +10848,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10854,10 +10859,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>20</v>
@@ -10866,20 +10871,20 @@
         <v>20</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -10928,19 +10933,19 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>20</v>
@@ -10949,10 +10954,10 @@
         <v>20</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
@@ -10963,10 +10968,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10974,10 +10979,10 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>20</v>
@@ -10986,20 +10991,20 @@
         <v>20</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -11009,7 +11014,7 @@
         <v>20</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>20</v>
@@ -11048,19 +11053,19 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>20</v>
@@ -11069,10 +11074,10 @@
         <v>20</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>20</v>
@@ -11083,10 +11088,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11094,10 +11099,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>20</v>
@@ -11106,22 +11111,22 @@
         <v>20</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -11131,7 +11136,7 @@
         <v>20</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>20</v>
@@ -11170,19 +11175,19 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>20</v>
@@ -11191,10 +11196,10 @@
         <v>20</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>20</v>
@@ -11205,10 +11210,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11216,10 +11221,10 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>20</v>
@@ -11231,19 +11236,19 @@
         <v>20</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -11268,13 +11273,13 @@
         <v>20</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>20</v>
@@ -11292,19 +11297,19 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>20</v>
@@ -11313,10 +11318,10 @@
         <v>20</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>20</v>
@@ -11327,21 +11332,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>20</v>
@@ -11353,19 +11358,19 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>20</v>
@@ -11390,13 +11395,13 @@
         <v>20</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>20</v>
@@ -11414,45 +11419,45 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11460,10 +11465,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>20</v>
@@ -11475,19 +11480,19 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>20</v>
@@ -11536,19 +11541,19 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>20</v>
@@ -11557,10 +11562,10 @@
         <v>20</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>20</v>
@@ -11571,23 +11576,23 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>20</v>
@@ -11596,22 +11601,22 @@
         <v>20</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>20</v>
@@ -11660,19 +11665,19 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>20</v>
@@ -11681,10 +11686,10 @@
         <v>20</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>20</v>
@@ -11695,10 +11700,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11706,10 +11711,10 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>20</v>
@@ -11721,13 +11726,13 @@
         <v>20</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11778,13 +11783,13 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>20</v>
@@ -11802,7 +11807,7 @@
         <v>20</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>20</v>
@@ -11813,21 +11818,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>20</v>
@@ -11839,16 +11844,16 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11898,19 +11903,19 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>20</v>
@@ -11922,7 +11927,7 @@
         <v>20</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>20</v>
@@ -11933,45 +11938,45 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -12020,19 +12025,19 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>20</v>
@@ -12044,7 +12049,7 @@
         <v>20</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>20</v>
@@ -12055,10 +12060,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12066,10 +12071,10 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>20</v>
@@ -12078,22 +12083,22 @@
         <v>20</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -12103,7 +12108,7 @@
         <v>20</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>20</v>
@@ -12118,13 +12123,13 @@
         <v>20</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>20</v>
@@ -12142,34 +12147,34 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>20</v>
@@ -12177,10 +12182,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12188,10 +12193,10 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>20</v>
@@ -12200,22 +12205,22 @@
         <v>20</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>20</v>
@@ -12264,45 +12269,45 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12310,10 +12315,10 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>20</v>
@@ -12325,13 +12330,13 @@
         <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12382,13 +12387,13 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>20</v>
@@ -12406,7 +12411,7 @@
         <v>20</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>20</v>
@@ -12417,21 +12422,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>20</v>
@@ -12443,16 +12448,16 @@
         <v>20</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12490,31 +12495,31 @@
         <v>20</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>20</v>
@@ -12526,7 +12531,7 @@
         <v>20</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>20</v>
@@ -12537,10 +12542,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12548,10 +12553,10 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>20</v>
@@ -12560,22 +12565,22 @@
         <v>20</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -12624,19 +12629,19 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>20</v>
@@ -12645,10 +12650,10 @@
         <v>20</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>20</v>
@@ -12659,10 +12664,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12670,38 +12675,38 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q88" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>20</v>
@@ -12722,13 +12727,13 @@
         <v>20</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>20</v>
@@ -12746,19 +12751,19 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>20</v>
@@ -12767,10 +12772,10 @@
         <v>20</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>20</v>
@@ -12781,10 +12786,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12792,10 +12797,10 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>20</v>
@@ -12804,20 +12809,20 @@
         <v>20</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>20</v>
@@ -12866,19 +12871,19 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>20</v>
@@ -12887,10 +12892,10 @@
         <v>20</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>20</v>
@@ -12901,10 +12906,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12912,10 +12917,10 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>20</v>
@@ -12924,20 +12929,20 @@
         <v>20</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -12947,7 +12952,7 @@
         <v>20</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>20</v>
@@ -12986,19 +12991,19 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>20</v>
@@ -13007,10 +13012,10 @@
         <v>20</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>20</v>
@@ -13021,10 +13026,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13032,10 +13037,10 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>20</v>
@@ -13044,22 +13049,22 @@
         <v>20</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>20</v>
@@ -13069,7 +13074,7 @@
         <v>20</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>20</v>
@@ -13108,19 +13113,19 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>20</v>
@@ -13129,10 +13134,10 @@
         <v>20</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>20</v>
@@ -13143,10 +13148,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13154,10 +13159,10 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>20</v>
@@ -13169,19 +13174,19 @@
         <v>20</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>20</v>
@@ -13206,13 +13211,13 @@
         <v>20</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>20</v>
@@ -13230,19 +13235,19 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>20</v>
@@ -13251,10 +13256,10 @@
         <v>20</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>20</v>
@@ -13265,21 +13270,21 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>20</v>
@@ -13291,19 +13296,19 @@
         <v>20</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>20</v>
@@ -13328,13 +13333,13 @@
         <v>20</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>20</v>
@@ -13352,45 +13357,45 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13398,10 +13403,10 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>20</v>
@@ -13413,19 +13418,19 @@
         <v>20</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>20</v>
@@ -13474,19 +13479,19 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>20</v>
@@ -13495,10 +13500,10 @@
         <v>20</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>20</v>
